--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,121 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129591670</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skoggylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>464059</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6255314</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539105</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129539106</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129591670</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539105</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129539106</v>
       </c>
       <c r="B3" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129591670</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539105</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129539106</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129591670</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539105</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129539106</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129591670</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>129591670</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44851-2025 artfynd.xlsx
+++ b/artfynd/A 44851-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539105</v>
+        <v>129539106</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -790,37 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539106</v>
+        <v>129539105</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -908,7 +908,7 @@
         <v>129591670</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
